--- a/reports/archive/2026-06-07/nasdaq100_qqq_daily_tracker_2026-06-07.xlsx
+++ b/reports/archive/2026-06-07/nasdaq100_qqq_daily_tracker_2026-06-07.xlsx
@@ -1939,7 +1939,7 @@
     <t>20/20 top20 quotes available; 10/10 top10 quotes available</t>
   </si>
   <si>
-    <t>98/98 symbols with history coverage; 20/98 history symbols with Twelve Data quote overlay; target_date=2026-06-05; target_aligned=88/98; non_target_aligned=10/98; min_latest_date=2026-06-04; max_latest_date=2026-06-05; target_date_source=current price_daily</t>
+    <t>98/98 symbols with history coverage; 20/98 history symbols with Twelve Data quote overlay; target_date=2026-06-05; target_aligned=98/98; non_target_aligned=0/98; min_latest_date=2026-06-05; max_latest_date=2026-06-05; target_date_source=current price_daily</t>
   </si>
   <si>
     <t>run_date</t>
@@ -2239,7 +2239,7 @@
     <t>weight coverage; rate_limited=False; fallback_provider=quote_cache</t>
   </si>
   <si>
-    <t>symbol coverage; ok=True; rows=8; message=98/98 symbols with history coverage; 20/98 history symbols with Twelve Data quote overlay; target_date=2026-06-05; target_aligned=88/98; non_target_aligned=10/98; min_latest_date=2026-06-04; max_latest_date=2026-06-05; target_date_source=current price_daily</t>
+    <t>symbol coverage; ok=True; rows=8; message=98/98 symbols with history coverage; 20/98 history symbols with Twelve Data quote overlay; target_date=2026-06-05; target_aligned=98/98; non_target_aligned=0/98; min_latest_date=2026-06-05; max_latest_date=2026-06-05; target_date_source=current price_daily</t>
   </si>
   <si>
     <t>weight coverage; rate_limited=False; fallback_provider=twelve_data_quote</t>
@@ -10783,7 +10783,7 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>28208</v>
+        <v>28218</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -12002,7 +12002,7 @@
         <v>556</v>
       </c>
       <c r="B31">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C31" t="s">
         <v>268</v>
@@ -12025,7 +12025,7 @@
         <v>557</v>
       </c>
       <c r="B32">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s">
         <v>268</v>
@@ -12048,7 +12048,7 @@
         <v>558</v>
       </c>
       <c r="B33">
-        <v>0.3673469387755102</v>
+        <v>0.3265306122448979</v>
       </c>
       <c r="C33" t="s">
         <v>268</v>
@@ -12071,7 +12071,7 @@
         <v>559</v>
       </c>
       <c r="B34">
-        <v>0.5102040816326531</v>
+        <v>0.4897959183673469</v>
       </c>
       <c r="C34" t="s">
         <v>268</v>
@@ -12094,7 +12094,7 @@
         <v>560</v>
       </c>
       <c r="B35">
-        <v>0.5204081632653061</v>
+        <v>0.5102040816326531</v>
       </c>
       <c r="C35" t="s">
         <v>268</v>
@@ -12117,7 +12117,7 @@
         <v>561</v>
       </c>
       <c r="B36">
-        <v>0.5816326530612245</v>
+        <v>0.5918367346938775</v>
       </c>
       <c r="C36" t="s">
         <v>268</v>
@@ -12140,7 +12140,7 @@
         <v>562</v>
       </c>
       <c r="B37">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C37" t="s">
         <v>268</v>
@@ -12163,7 +12163,7 @@
         <v>563</v>
       </c>
       <c r="B38">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C38" t="s">
         <v>268</v>
@@ -18577,7 +18577,7 @@
         <v>556</v>
       </c>
       <c r="B2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>98</v>
@@ -18597,7 +18597,7 @@
         <v>557</v>
       </c>
       <c r="B3">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C3">
         <v>98</v>
@@ -18617,7 +18617,7 @@
         <v>558</v>
       </c>
       <c r="B4">
-        <v>0.3673469387755102</v>
+        <v>0.3265306122448979</v>
       </c>
       <c r="C4">
         <v>98</v>
@@ -18637,7 +18637,7 @@
         <v>559</v>
       </c>
       <c r="B5">
-        <v>0.5102040816326531</v>
+        <v>0.4897959183673469</v>
       </c>
       <c r="C5">
         <v>98</v>
@@ -18657,7 +18657,7 @@
         <v>560</v>
       </c>
       <c r="B6">
-        <v>0.5204081632653061</v>
+        <v>0.5102040816326531</v>
       </c>
       <c r="C6">
         <v>98</v>
@@ -18677,7 +18677,7 @@
         <v>561</v>
       </c>
       <c r="B7">
-        <v>0.5816326530612245</v>
+        <v>0.5918367346938775</v>
       </c>
       <c r="C7">
         <v>98</v>
@@ -18697,7 +18697,7 @@
         <v>562</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>98</v>
@@ -18717,7 +18717,7 @@
         <v>563</v>
       </c>
       <c r="B9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9">
         <v>98</v>
